--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -1153,333 +1153,272 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="8.87272727272727" style="1"/>
-    <col min="2" max="2" width="19.3727272727273" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7545454545455" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="5" width="52.1818181818182" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.87272727272727" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="B4" s="1">
-        <v>801</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5" s="1">
-        <v>802</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="1">
-        <v>803</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="1">
-        <v>901</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="1">
-        <v>902</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="1">
-        <v>903</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="3">
-        <v>100</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="3">
-        <v>101</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="3">
-        <v>102</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:H14"/>
+  <ns0:sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="7"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="8.87272727272727" style="1"/>
+    <ns0:col min="2" max="2" width="19.3727272727273" style="1" customWidth="1"/>
+    <ns0:col min="3" max="3" width="20.7545454545455" style="1" customWidth="1"/>
+    <ns0:col min="4" max="4" width="22" style="1" customWidth="1"/>
+    <ns0:col min="5" max="5" width="52.1818181818182" style="1" customWidth="1"/>
+    <ns0:col min="6" max="6" width="14.6272727272727" style="1" customWidth="1"/>
+    <ns0:col min="7" max="7" width="23.1272727272727" style="1" customWidth="1"/>
+    <ns0:col min="8" max="8" width="23" style="1" customWidth="1"/>
+    <ns0:col min="9" max="16384" width="8.87272727272727" style="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" spans="1:8">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="1" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="1" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="1" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="1" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="1" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" spans="1:8">
+      <ns0:c r="A2" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="1" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="1" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="1" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="1" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" spans="1:8">
+      <ns0:c r="A3" s="2" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="2" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="1" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="2" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="1" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="2" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="1" t="s">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" spans="1:8">
+      <ns0:c r="B4" s="1">
+        <ns0:v>801</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="1" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="1" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="1" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="1" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5" spans="1:8">
+      <ns0:c r="B5" s="1">
+        <ns0:v>802</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="1" t="s">
+        <ns0:v>26</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="1" t="s">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="1" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5" s="1" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="G5" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6" spans="1:8">
+      <ns0:c r="B6" s="1">
+        <ns0:v>803</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="1" t="s">
+        <ns0:v>29</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="1" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="1" t="s">
+        <ns0:v>31</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="1" t="s">
+        <ns0:v>32</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7" spans="1:8">
+      <ns0:c r="B7" s="1">
+        <ns0:v>901</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="1" t="s">
+        <ns0:v>33</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="1" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="1" t="s">
+        <ns0:v>34</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="1" t="s">
+        <ns0:v>32</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8" spans="1:8">
+      <ns0:c r="B8" s="1">
+        <ns0:v>902</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="1" t="s">
+        <ns0:v>35</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="1" t="s">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="1" t="s">
+        <ns0:v>36</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="1" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="G8" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H8" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9" spans="1:8">
+      <ns0:c r="B9" s="1">
+        <ns0:v>903</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="1" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="1" t="s">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="1" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="1" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="G9" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9" s="1" t="b">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14" spans="1:8">
+      <ns0:c r="B14" s="3">
+        <ns0:v>1101</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UIGridKitchen</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D14" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>格子厨房操作界面</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E14" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Product/UIGridKitchen</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F14" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Default</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G14" s="3">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H14" s="3">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:pageSetup paperSize="9" orientation="portrait"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>